--- a/data/هدیش.xlsx
+++ b/data/هدیش.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\v.pishdad\Downloads\برنامه ها فروشگاه ها\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a.farshchian\Desktop\New folder (4)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16095745-E9BB-4C4D-8EF7-8865BB017A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF572CC-DF19-4A9C-A809-8A93CBFEEBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="1980" windowWidth="21600" windowHeight="10815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="فرم آدیت" sheetId="1" r:id="rId1"/>
+    <sheet name="هدیش 14ام" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,15 +34,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="83">
   <si>
     <t>نام فروشگاه</t>
   </si>
   <si>
-    <t>ماه</t>
-  </si>
-  <si>
-    <t>سال</t>
+    <t>تاریخ آدیت</t>
   </si>
   <si>
     <t>ارزیاب</t>
@@ -277,12 +274,24 @@
   </si>
   <si>
     <t>In Process</t>
+  </si>
+  <si>
+    <t>وحید پیشداد</t>
+  </si>
+  <si>
+    <t>1405/05/14</t>
+  </si>
+  <si>
+    <t>هدیش</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <sz val="11"/>
@@ -500,7 +509,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -517,20 +526,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -790,9 +802,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{845567EB-BB4F-47CE-AD53-0760849E4BB3}">
   <dimension ref="A1:F67"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -802,63 +814,67 @@
     <col min="6" max="6" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="34.049999999999997" customHeight="1">
-      <c r="A1" s="11" t="str">
+    <row r="1" spans="1:6" ht="33.950000000000003" customHeight="1">
+      <c r="A1" s="12" t="str">
         <f>IF(B2="","فرم ارزیابی دوره‌ای فروشگاه","ارزیابی فروشگاه "&amp;B2&amp;" — "&amp;D2&amp;" "&amp;F2)</f>
-        <v>فرم ارزیابی دوره‌ای فروشگاه</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-    </row>
-    <row r="2" spans="1:6">
+        <v xml:space="preserve">ارزیابی فروشگاه هدیش — 1405/05/14 </v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+    </row>
+    <row r="2" spans="1:6" ht="15">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" ht="15">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2"/>
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1">
       <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="27" customHeight="1">
@@ -866,147 +882,147 @@
         <v>101</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="6">
-        <v>1</v>
-      </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="8"/>
+      <c r="D6" s="9">
+        <v>1</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="11"/>
     </row>
     <row r="7" spans="1:6" ht="27" customHeight="1">
       <c r="A7" s="4">
         <v>101</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="6">
-        <v>1</v>
-      </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
+        <v>13</v>
+      </c>
+      <c r="D7" s="9">
+        <v>1</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="11"/>
     </row>
     <row r="8" spans="1:6" ht="27" customHeight="1">
       <c r="A8" s="4">
         <v>101</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="6">
-        <v>1</v>
-      </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8"/>
+        <v>14</v>
+      </c>
+      <c r="D8" s="9">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10"/>
+      <c r="F8" s="11"/>
     </row>
     <row r="9" spans="1:6" ht="27" customHeight="1">
       <c r="A9" s="4">
         <v>101</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="6">
-        <v>1</v>
-      </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="8"/>
+        <v>15</v>
+      </c>
+      <c r="D9" s="9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="11"/>
     </row>
     <row r="10" spans="1:6" ht="27" customHeight="1">
       <c r="A10" s="4">
         <v>101</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="6">
-        <v>1</v>
-      </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="8"/>
+        <v>16</v>
+      </c>
+      <c r="D10" s="9">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="F10" s="11"/>
     </row>
     <row r="11" spans="1:6" ht="27" customHeight="1">
       <c r="A11" s="4">
         <v>101</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="6">
-        <v>1</v>
-      </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="8"/>
+        <v>17</v>
+      </c>
+      <c r="D11" s="9">
+        <v>1</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="11"/>
     </row>
     <row r="12" spans="1:6" ht="27" customHeight="1">
       <c r="A12" s="4">
         <v>101</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="6">
-        <v>1</v>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="D12" s="9">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10"/>
+      <c r="F12" s="11"/>
     </row>
     <row r="13" spans="1:6" ht="27" customHeight="1">
       <c r="A13" s="4">
         <v>101</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="6">
-        <v>1</v>
-      </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="8"/>
+        <v>19</v>
+      </c>
+      <c r="D13" s="9">
+        <v>1</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="11"/>
     </row>
     <row r="14" spans="1:6" ht="27" customHeight="1">
       <c r="A14" s="4">
         <v>101</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="6">
+        <v>20</v>
+      </c>
+      <c r="D14" s="9">
         <v>0</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="11" t="s">
         <v>78</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="27" customHeight="1">
@@ -1014,789 +1030,789 @@
         <v>101</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="6">
-        <v>1</v>
-      </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="8"/>
+        <v>21</v>
+      </c>
+      <c r="D15" s="9">
+        <v>1</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="11"/>
     </row>
     <row r="16" spans="1:6" ht="27" customHeight="1">
       <c r="A16" s="4">
         <v>101</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="6">
-        <v>1</v>
-      </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="8"/>
+        <v>22</v>
+      </c>
+      <c r="D16" s="9">
+        <v>1</v>
+      </c>
+      <c r="E16" s="10"/>
+      <c r="F16" s="11"/>
     </row>
     <row r="17" spans="1:6" ht="27" customHeight="1">
       <c r="A17" s="4">
         <v>102</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="6">
-        <v>1</v>
-      </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="8"/>
+      <c r="D17" s="9">
+        <v>1</v>
+      </c>
+      <c r="E17" s="10"/>
+      <c r="F17" s="11"/>
     </row>
     <row r="18" spans="1:6" ht="27" customHeight="1">
       <c r="A18" s="4">
         <v>102</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="6">
-        <v>1</v>
-      </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="8"/>
+        <v>25</v>
+      </c>
+      <c r="D18" s="9">
+        <v>1</v>
+      </c>
+      <c r="E18" s="10"/>
+      <c r="F18" s="11"/>
     </row>
     <row r="19" spans="1:6" ht="27" customHeight="1">
       <c r="A19" s="4">
         <v>102</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19" s="6">
-        <v>1</v>
-      </c>
-      <c r="E19" s="7"/>
-      <c r="F19" s="8"/>
+        <v>26</v>
+      </c>
+      <c r="D19" s="9">
+        <v>1</v>
+      </c>
+      <c r="E19" s="10"/>
+      <c r="F19" s="11"/>
     </row>
     <row r="20" spans="1:6" ht="27" customHeight="1">
       <c r="A20" s="4">
         <v>102</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="6">
-        <v>1</v>
-      </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="8"/>
+        <v>27</v>
+      </c>
+      <c r="D20" s="9">
+        <v>1</v>
+      </c>
+      <c r="E20" s="10"/>
+      <c r="F20" s="11"/>
     </row>
     <row r="21" spans="1:6" ht="27" customHeight="1">
       <c r="A21" s="4">
         <v>102</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="6">
-        <v>1</v>
-      </c>
-      <c r="E21" s="7"/>
-      <c r="F21" s="8"/>
+        <v>28</v>
+      </c>
+      <c r="D21" s="9">
+        <v>1</v>
+      </c>
+      <c r="E21" s="10"/>
+      <c r="F21" s="11"/>
     </row>
     <row r="22" spans="1:6" ht="27" customHeight="1">
       <c r="A22" s="4">
         <v>102</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="6">
+        <v>29</v>
+      </c>
+      <c r="D22" s="9">
         <v>0</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F22" s="8"/>
+      <c r="E22" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" s="11"/>
     </row>
     <row r="23" spans="1:6" ht="27" customHeight="1">
       <c r="A23" s="4">
         <v>102</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="6">
-        <v>1</v>
-      </c>
-      <c r="E23" s="7"/>
-      <c r="F23" s="8"/>
+        <v>30</v>
+      </c>
+      <c r="D23" s="9">
+        <v>1</v>
+      </c>
+      <c r="E23" s="10"/>
+      <c r="F23" s="11"/>
     </row>
     <row r="24" spans="1:6" ht="27" customHeight="1">
       <c r="A24" s="4">
         <v>102</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="6">
-        <v>1</v>
-      </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="8"/>
+        <v>31</v>
+      </c>
+      <c r="D24" s="9">
+        <v>1</v>
+      </c>
+      <c r="E24" s="10"/>
+      <c r="F24" s="11"/>
     </row>
     <row r="25" spans="1:6" ht="27" customHeight="1">
       <c r="A25" s="4">
         <v>102</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" s="6">
-        <v>1</v>
-      </c>
-      <c r="E25" s="7"/>
-      <c r="F25" s="8"/>
+        <v>32</v>
+      </c>
+      <c r="D25" s="9">
+        <v>1</v>
+      </c>
+      <c r="E25" s="10"/>
+      <c r="F25" s="11"/>
     </row>
     <row r="26" spans="1:6" ht="27" customHeight="1">
       <c r="A26" s="4">
         <v>103</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" s="6">
-        <v>1</v>
-      </c>
-      <c r="E26" s="7"/>
-      <c r="F26" s="8"/>
+      <c r="D26" s="9">
+        <v>1</v>
+      </c>
+      <c r="E26" s="10"/>
+      <c r="F26" s="11"/>
     </row>
     <row r="27" spans="1:6" ht="27" customHeight="1">
       <c r="A27" s="4">
         <v>103</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D27" s="6">
-        <v>1</v>
-      </c>
-      <c r="E27" s="7"/>
-      <c r="F27" s="8"/>
+        <v>35</v>
+      </c>
+      <c r="D27" s="9">
+        <v>1</v>
+      </c>
+      <c r="E27" s="10"/>
+      <c r="F27" s="11"/>
     </row>
     <row r="28" spans="1:6" ht="27" customHeight="1">
       <c r="A28" s="4">
         <v>103</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" s="6">
-        <v>1</v>
-      </c>
-      <c r="E28" s="7"/>
-      <c r="F28" s="8"/>
+        <v>36</v>
+      </c>
+      <c r="D28" s="9">
+        <v>1</v>
+      </c>
+      <c r="E28" s="10"/>
+      <c r="F28" s="11"/>
     </row>
     <row r="29" spans="1:6" ht="27" customHeight="1">
       <c r="A29" s="4">
         <v>103</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D29" s="6">
-        <v>1</v>
-      </c>
-      <c r="E29" s="7"/>
-      <c r="F29" s="8"/>
+        <v>37</v>
+      </c>
+      <c r="D29" s="9">
+        <v>1</v>
+      </c>
+      <c r="E29" s="10"/>
+      <c r="F29" s="11"/>
     </row>
     <row r="30" spans="1:6" ht="27" customHeight="1">
       <c r="A30" s="4">
         <v>103</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D30" s="6">
-        <v>1</v>
-      </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="8"/>
+        <v>38</v>
+      </c>
+      <c r="D30" s="9">
+        <v>1</v>
+      </c>
+      <c r="E30" s="10"/>
+      <c r="F30" s="11"/>
     </row>
     <row r="31" spans="1:6" ht="27" customHeight="1">
       <c r="A31" s="4">
         <v>103</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D31" s="6">
-        <v>1</v>
-      </c>
-      <c r="E31" s="7"/>
-      <c r="F31" s="8"/>
+        <v>39</v>
+      </c>
+      <c r="D31" s="9">
+        <v>1</v>
+      </c>
+      <c r="E31" s="10"/>
+      <c r="F31" s="11"/>
     </row>
     <row r="32" spans="1:6" ht="27" customHeight="1">
       <c r="A32" s="4">
         <v>103</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D32" s="6">
-        <v>1</v>
-      </c>
-      <c r="E32" s="7"/>
-      <c r="F32" s="8"/>
+        <v>40</v>
+      </c>
+      <c r="D32" s="9">
+        <v>1</v>
+      </c>
+      <c r="E32" s="10"/>
+      <c r="F32" s="11"/>
     </row>
     <row r="33" spans="1:6" ht="27" customHeight="1">
       <c r="A33" s="4">
         <v>103</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D33" s="6">
-        <v>1</v>
-      </c>
-      <c r="E33" s="7"/>
-      <c r="F33" s="8"/>
+        <v>41</v>
+      </c>
+      <c r="D33" s="9">
+        <v>1</v>
+      </c>
+      <c r="E33" s="10"/>
+      <c r="F33" s="11"/>
     </row>
     <row r="34" spans="1:6" ht="27" customHeight="1">
       <c r="A34" s="4">
         <v>104</v>
       </c>
       <c r="B34" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" s="6">
-        <v>1</v>
-      </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="8"/>
+      <c r="D34" s="9">
+        <v>1</v>
+      </c>
+      <c r="E34" s="10"/>
+      <c r="F34" s="11"/>
     </row>
     <row r="35" spans="1:6" ht="27" customHeight="1">
       <c r="A35" s="4">
         <v>104</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D35" s="6">
-        <v>1</v>
-      </c>
-      <c r="E35" s="7"/>
-      <c r="F35" s="8"/>
+        <v>44</v>
+      </c>
+      <c r="D35" s="9">
+        <v>1</v>
+      </c>
+      <c r="E35" s="10"/>
+      <c r="F35" s="11"/>
     </row>
     <row r="36" spans="1:6" ht="27" customHeight="1">
       <c r="A36" s="4">
         <v>104</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D36" s="6">
-        <v>1</v>
-      </c>
-      <c r="E36" s="7"/>
-      <c r="F36" s="8"/>
+        <v>45</v>
+      </c>
+      <c r="D36" s="9">
+        <v>1</v>
+      </c>
+      <c r="E36" s="10"/>
+      <c r="F36" s="11"/>
     </row>
     <row r="37" spans="1:6" ht="27" customHeight="1">
       <c r="A37" s="4">
         <v>104</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D37" s="6">
-        <v>1</v>
-      </c>
-      <c r="E37" s="7"/>
-      <c r="F37" s="8"/>
+        <v>46</v>
+      </c>
+      <c r="D37" s="9">
+        <v>1</v>
+      </c>
+      <c r="E37" s="10"/>
+      <c r="F37" s="11"/>
     </row>
     <row r="38" spans="1:6" ht="27" customHeight="1">
       <c r="A38" s="4">
         <v>104</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D38" s="6">
-        <v>1</v>
-      </c>
-      <c r="E38" s="7"/>
-      <c r="F38" s="8"/>
+        <v>47</v>
+      </c>
+      <c r="D38" s="9">
+        <v>1</v>
+      </c>
+      <c r="E38" s="10"/>
+      <c r="F38" s="11"/>
     </row>
     <row r="39" spans="1:6" ht="27" customHeight="1">
       <c r="A39" s="4">
         <v>104</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D39" s="6">
-        <v>1</v>
-      </c>
-      <c r="E39" s="7"/>
-      <c r="F39" s="8"/>
+        <v>48</v>
+      </c>
+      <c r="D39" s="9">
+        <v>1</v>
+      </c>
+      <c r="E39" s="10"/>
+      <c r="F39" s="11"/>
     </row>
     <row r="40" spans="1:6" ht="27" customHeight="1">
       <c r="A40" s="4">
         <v>104</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D40" s="6">
-        <v>1</v>
-      </c>
-      <c r="E40" s="7"/>
-      <c r="F40" s="8"/>
+        <v>49</v>
+      </c>
+      <c r="D40" s="9">
+        <v>1</v>
+      </c>
+      <c r="E40" s="10"/>
+      <c r="F40" s="11"/>
     </row>
     <row r="41" spans="1:6" ht="27" customHeight="1">
       <c r="A41" s="4">
         <v>104</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D41" s="6">
-        <v>1</v>
-      </c>
-      <c r="E41" s="7"/>
-      <c r="F41" s="8"/>
+        <v>50</v>
+      </c>
+      <c r="D41" s="9">
+        <v>1</v>
+      </c>
+      <c r="E41" s="10"/>
+      <c r="F41" s="11"/>
     </row>
     <row r="42" spans="1:6" ht="27" customHeight="1">
       <c r="A42" s="4">
         <v>105</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D42" s="6">
-        <v>1</v>
-      </c>
-      <c r="E42" s="7"/>
-      <c r="F42" s="8"/>
+      <c r="D42" s="9">
+        <v>1</v>
+      </c>
+      <c r="E42" s="10"/>
+      <c r="F42" s="11"/>
     </row>
     <row r="43" spans="1:6" ht="27" customHeight="1">
       <c r="A43" s="4">
         <v>105</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D43" s="6">
-        <v>1</v>
-      </c>
-      <c r="E43" s="7"/>
-      <c r="F43" s="8"/>
+        <v>53</v>
+      </c>
+      <c r="D43" s="9">
+        <v>1</v>
+      </c>
+      <c r="E43" s="10"/>
+      <c r="F43" s="11"/>
     </row>
     <row r="44" spans="1:6" ht="27" customHeight="1">
       <c r="A44" s="4">
         <v>105</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D44" s="6">
-        <v>1</v>
-      </c>
-      <c r="E44" s="7"/>
-      <c r="F44" s="8"/>
+        <v>54</v>
+      </c>
+      <c r="D44" s="9">
+        <v>1</v>
+      </c>
+      <c r="E44" s="10"/>
+      <c r="F44" s="11"/>
     </row>
     <row r="45" spans="1:6" ht="27" customHeight="1">
       <c r="A45" s="4">
         <v>105</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D45" s="6">
-        <v>1</v>
-      </c>
-      <c r="E45" s="7"/>
-      <c r="F45" s="8"/>
+        <v>55</v>
+      </c>
+      <c r="D45" s="9">
+        <v>1</v>
+      </c>
+      <c r="E45" s="10"/>
+      <c r="F45" s="11"/>
     </row>
     <row r="46" spans="1:6" ht="27" customHeight="1">
       <c r="A46" s="4">
         <v>105</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D46" s="6">
-        <v>1</v>
-      </c>
-      <c r="E46" s="7"/>
-      <c r="F46" s="8"/>
+        <v>56</v>
+      </c>
+      <c r="D46" s="9">
+        <v>1</v>
+      </c>
+      <c r="E46" s="10"/>
+      <c r="F46" s="11"/>
     </row>
     <row r="47" spans="1:6" ht="27" customHeight="1">
       <c r="A47" s="4">
         <v>105</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D47" s="6">
-        <v>1</v>
-      </c>
-      <c r="E47" s="7"/>
-      <c r="F47" s="8"/>
+        <v>57</v>
+      </c>
+      <c r="D47" s="9">
+        <v>1</v>
+      </c>
+      <c r="E47" s="10"/>
+      <c r="F47" s="11"/>
     </row>
     <row r="48" spans="1:6" ht="27" customHeight="1">
       <c r="A48" s="4">
         <v>105</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D48" s="6">
-        <v>1</v>
-      </c>
-      <c r="E48" s="7"/>
-      <c r="F48" s="8"/>
+        <v>58</v>
+      </c>
+      <c r="D48" s="9">
+        <v>1</v>
+      </c>
+      <c r="E48" s="10"/>
+      <c r="F48" s="11"/>
     </row>
     <row r="49" spans="1:6" ht="27" customHeight="1">
       <c r="A49" s="4">
         <v>105</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D49" s="6">
-        <v>1</v>
-      </c>
-      <c r="E49" s="7"/>
-      <c r="F49" s="8"/>
+        <v>59</v>
+      </c>
+      <c r="D49" s="9">
+        <v>1</v>
+      </c>
+      <c r="E49" s="10"/>
+      <c r="F49" s="11"/>
     </row>
     <row r="50" spans="1:6" ht="27" customHeight="1">
       <c r="A50" s="4">
         <v>106</v>
       </c>
       <c r="B50" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D50" s="6">
-        <v>1</v>
-      </c>
-      <c r="E50" s="7"/>
-      <c r="F50" s="8"/>
+      <c r="D50" s="9">
+        <v>1</v>
+      </c>
+      <c r="E50" s="10"/>
+      <c r="F50" s="11"/>
     </row>
     <row r="51" spans="1:6" ht="27" customHeight="1">
       <c r="A51" s="4">
         <v>106</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D51" s="6">
-        <v>1</v>
-      </c>
-      <c r="E51" s="7"/>
-      <c r="F51" s="8"/>
+        <v>62</v>
+      </c>
+      <c r="D51" s="9">
+        <v>1</v>
+      </c>
+      <c r="E51" s="10"/>
+      <c r="F51" s="11"/>
     </row>
     <row r="52" spans="1:6" ht="27" customHeight="1">
       <c r="A52" s="4">
         <v>106</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D52" s="6">
-        <v>1</v>
-      </c>
-      <c r="E52" s="7"/>
-      <c r="F52" s="8"/>
+        <v>63</v>
+      </c>
+      <c r="D52" s="9">
+        <v>1</v>
+      </c>
+      <c r="E52" s="10"/>
+      <c r="F52" s="11"/>
     </row>
     <row r="53" spans="1:6" ht="27" customHeight="1">
       <c r="A53" s="4">
         <v>106</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D53" s="6">
-        <v>1</v>
-      </c>
-      <c r="E53" s="7"/>
-      <c r="F53" s="8"/>
+        <v>64</v>
+      </c>
+      <c r="D53" s="9">
+        <v>1</v>
+      </c>
+      <c r="E53" s="10"/>
+      <c r="F53" s="11"/>
     </row>
     <row r="54" spans="1:6" ht="27" customHeight="1">
       <c r="A54" s="4">
         <v>106</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D54" s="6">
-        <v>1</v>
-      </c>
-      <c r="E54" s="7"/>
-      <c r="F54" s="8"/>
+        <v>65</v>
+      </c>
+      <c r="D54" s="9">
+        <v>1</v>
+      </c>
+      <c r="E54" s="10"/>
+      <c r="F54" s="11"/>
     </row>
     <row r="55" spans="1:6" ht="27" customHeight="1">
       <c r="A55" s="4">
         <v>106</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D55" s="6">
-        <v>1</v>
-      </c>
-      <c r="E55" s="7"/>
-      <c r="F55" s="8"/>
+        <v>66</v>
+      </c>
+      <c r="D55" s="9">
+        <v>1</v>
+      </c>
+      <c r="E55" s="10"/>
+      <c r="F55" s="11"/>
     </row>
     <row r="56" spans="1:6" ht="27" customHeight="1">
       <c r="A56" s="4">
         <v>107</v>
       </c>
       <c r="B56" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C56" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D56" s="6">
-        <v>1</v>
-      </c>
-      <c r="E56" s="7"/>
-      <c r="F56" s="8"/>
+      <c r="D56" s="9">
+        <v>1</v>
+      </c>
+      <c r="E56" s="10"/>
+      <c r="F56" s="11"/>
     </row>
     <row r="57" spans="1:6" ht="27" customHeight="1">
       <c r="A57" s="4">
         <v>107</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D57" s="6">
-        <v>1</v>
-      </c>
-      <c r="E57" s="7"/>
-      <c r="F57" s="8"/>
+        <v>69</v>
+      </c>
+      <c r="D57" s="9">
+        <v>1</v>
+      </c>
+      <c r="E57" s="10"/>
+      <c r="F57" s="11"/>
     </row>
     <row r="58" spans="1:6" ht="27" customHeight="1">
       <c r="A58" s="4">
         <v>107</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D58" s="6">
-        <v>1</v>
-      </c>
-      <c r="E58" s="7"/>
-      <c r="F58" s="8"/>
+        <v>70</v>
+      </c>
+      <c r="D58" s="9">
+        <v>1</v>
+      </c>
+      <c r="E58" s="10"/>
+      <c r="F58" s="11"/>
     </row>
     <row r="59" spans="1:6" ht="27" customHeight="1">
       <c r="A59" s="4">
         <v>107</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D59" s="6">
-        <v>1</v>
-      </c>
-      <c r="E59" s="7"/>
-      <c r="F59" s="8"/>
+        <v>71</v>
+      </c>
+      <c r="D59" s="9">
+        <v>1</v>
+      </c>
+      <c r="E59" s="10"/>
+      <c r="F59" s="11"/>
     </row>
     <row r="60" spans="1:6" ht="27" customHeight="1">
       <c r="A60" s="4">
         <v>107</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C60" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D60" s="9">
+        <v>1</v>
+      </c>
+      <c r="E60" s="10"/>
+      <c r="F60" s="11"/>
+    </row>
+    <row r="62" spans="1:6" ht="15">
+      <c r="A62" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D60" s="6">
-        <v>1</v>
-      </c>
-      <c r="E60" s="7"/>
-      <c r="F60" s="8"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="9">
+      <c r="B62" s="13"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="8">
         <f>SUM(D6:D60)</f>
         <v>53</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
-      <c r="A63" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B63" s="12"/>
-      <c r="C63" s="12"/>
-      <c r="D63" s="9">
+    <row r="63" spans="1:6" ht="15">
+      <c r="A63" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B63" s="13"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="8">
         <f>COUNTA(A6:A60)</f>
         <v>55</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
-      <c r="A64" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B64" s="12"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="10">
+    <row r="64" spans="1:6" ht="15">
+      <c r="A64" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B64" s="13"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="6">
         <f>IF(D63=0,0,D62/D63)</f>
         <v>0.96363636363636362</v>
       </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="15"/>
+      <c r="A66" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B66" s="15"/>
+      <c r="C66" s="15"/>
+      <c r="D66" s="15"/>
+      <c r="E66" s="15"/>
+      <c r="F66" s="16"/>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="16"/>
-      <c r="B67" s="17"/>
-      <c r="C67" s="17"/>
-      <c r="D67" s="17"/>
-      <c r="E67" s="17"/>
-      <c r="F67" s="18"/>
+      <c r="A67" s="17"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="18"/>
+      <c r="E67" s="18"/>
+      <c r="F67" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1815,14 +1831,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" sqref="D2" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"فروردین,اردیبهشت,خرداد,تیر,مرداد,شهریور,مهر,آبان,آذر,دی,بهمن,اسفند"</formula1>
+    <dataValidation type="list" sqref="E6:E60" xr:uid="{2325E09B-007B-4B7F-8608-D68D6CE33137}">
+      <formula1>"To Do,In Process,Done"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D6:D60" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="D6:D60" xr:uid="{B4E431CD-617F-4499-BC10-7B384209AA24}">
       <formula1>"0,1"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E6:E60" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>"To Do,In Process,Done"</formula1>
+    <dataValidation type="list" sqref="D2" xr:uid="{CC4E2BB9-4360-46D4-B815-47D035EB4A24}">
+      <formula1>"فروردین,اردیبهشت,خرداد,تیر,مرداد,شهریور,مهر,آبان,آذر,دی,بهمن,اسفند"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
